--- a/wordstat/output/2026-09-15-top/wordstat_top.xlsx
+++ b/wordstat/output/2026-09-15-top/wordstat_top.xlsx
@@ -15,6 +15,14 @@
     <sheet name="овсянников купить ассоциации" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="овсянников крем" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="овсянников крем ассоциации" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="овсянников сайт" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="овсянников сайт ассоциации" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="овсянников тайный советник" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="овсянников тайный советник ассо" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ovsyannikovsoap" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ovsyannikovsoap ассоциации" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ovsyannikov" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ovsyannikov ассоциации" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -841,6 +849,3444 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ассоциация</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тюменская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Волгоградская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Мордовия</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Орловская область</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Рязанская область</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Ярославская область</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Костромская область</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Новосибирская область</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Саратовская область</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Томская область</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Вологодская область</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Алтайский край</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Омская область</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Кемеровская область</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Кировская область</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Пензенская область</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Ростовская область</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Тульская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>веб страница это</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1879</v>
+      </c>
+      <c r="D2" t="n">
+        <v>261</v>
+      </c>
+      <c r="G2" t="n">
+        <v>48</v>
+      </c>
+      <c r="H2" t="n">
+        <v>41</v>
+      </c>
+      <c r="I2" t="n">
+        <v>67</v>
+      </c>
+      <c r="K2" t="n">
+        <v>330</v>
+      </c>
+      <c r="L2" t="n">
+        <v>209</v>
+      </c>
+      <c r="P2" t="n">
+        <v>110</v>
+      </c>
+      <c r="R2" t="n">
+        <v>219</v>
+      </c>
+      <c r="T2" t="n">
+        <v>65</v>
+      </c>
+      <c r="U2" t="n">
+        <v>490</v>
+      </c>
+      <c r="V2" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>веб портал</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>979</v>
+      </c>
+      <c r="D3" t="n">
+        <v>164</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I3" t="n">
+        <v>34</v>
+      </c>
+      <c r="K3" t="n">
+        <v>163</v>
+      </c>
+      <c r="L3" t="n">
+        <v>115</v>
+      </c>
+      <c r="P3" t="n">
+        <v>61</v>
+      </c>
+      <c r="R3" t="n">
+        <v>88</v>
+      </c>
+      <c r="T3" t="n">
+        <v>32</v>
+      </c>
+      <c r="U3" t="n">
+        <v>259</v>
+      </c>
+      <c r="V3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>столички официальный сайт</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>196</v>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4pda официальный сайт</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>165</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ожнокласники ру моя страница</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>123</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>92</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>рциот официальный сайт</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>122</v>
+      </c>
+      <c r="C7" t="n">
+        <v>39</v>
+      </c>
+      <c r="E7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>миуз официальный сайт</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>99</v>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https ya ruодноклассники моя страничка</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>95</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>11</v>
+      </c>
+      <c r="U9" t="n">
+        <v>36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>нфмо портал личный кабинет</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>94</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>41</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>6</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ямк официальный сайт</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C11" t="n">
+        <v>87</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>эссевен официальный сайт</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>78</v>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>юду ру официальный сайт</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>74</v>
+      </c>
+      <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>биодерма официальный сайт</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>71</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>29</v>
+      </c>
+      <c r="N14" t="n">
+        <v>22</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>эсф портал</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>48</v>
+      </c>
+      <c r="P15" t="n">
+        <v>6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>incy официальный сайт</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>51</v>
+      </c>
+      <c r="C16" t="n">
+        <v>16</v>
+      </c>
+      <c r="E16" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>портал мыюа</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>37</v>
+      </c>
+      <c r="D17" t="n">
+        <v>17</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>xhwebsite com</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>36</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>23</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>адноклассника ру моя страница</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>учз официальный сайт</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>36</v>
+      </c>
+      <c r="C20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>фармакосметика официальный сайт</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>36</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13</v>
+      </c>
+      <c r="O21" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>портал улгу</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>34</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bmai официальный сайт</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>29</v>
+      </c>
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>n8n официальный сайт</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>29</v>
+      </c>
+      <c r="C24" t="n">
+        <v>13</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>плеяна косметика официальный</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>уига официальный сайт</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>20</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mesomatrix официальный сайт</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>14</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>барс добровольцы официальный сайт</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>14</v>
+      </c>
+      <c r="S28" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bioderma официальный сайт</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>12</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>icon skin официальный сайт</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>мыц официальный сайт</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>твоятерритория ру онлайн</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>фитокосметик официальный сайт</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>11</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>limba cosmetics официальный сайт</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>безкомплексов ру моя страница</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>тгасу официальный сайт</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>янссен косметикс официальный сайт</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>9</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>unode50 официальный сайт</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>зеленое яблоко интернет магазин официальный</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="S39" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sasha cosmetics официальный сайт</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>улгу официальный сайт</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>арнокосметик официальный сайт</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>екту портал</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>veritate cosmetics официальный сайт</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>портал ииас</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>сиберика косметика официальный интернет магазин</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ямогочи официальный сайт</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>nikk mole официальный сайт</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>smorodina косметика официальный сайт</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>аравиа официальный сайт</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>цимус официальный сайт</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>amouage официальный сайт</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>biomio официальный сайт</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>жемчужины мысли официальный сайт</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>созвездие красоты интернет магазин официальный сайт</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>эсф портал вход</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Вложенный запрос</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Рязанская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Ярославская область</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Костромская область</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Ивановская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>овсянников тайный советник</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>диффузор овсянников тайный советник</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>овсянников тайный советник крем</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ассоциация</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Рязанская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Ярославская область</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Костромская область</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Ивановская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>секретное досье</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>273</v>
+      </c>
+      <c r="C2" t="n">
+        <v>176</v>
+      </c>
+      <c r="D2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>елизавета значение</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>196</v>
+      </c>
+      <c r="C3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>кузькина елена викторовна</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>185</v>
+      </c>
+      <c r="C4" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>помощник следователя</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>140</v>
+      </c>
+      <c r="C5" t="n">
+        <v>89</v>
+      </c>
+      <c r="D5" t="n">
+        <v>27</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>особая молитвенная помощь сергей пономарь</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>55</v>
+      </c>
+      <c r="C6" t="n">
+        <v>43</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>станционный смотритель основная мысль</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>секта скопцов</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>офицер особого назначения аудиокнига слушать</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ревизор основная мысль</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>сообщница злодея книга</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>галактический отбор помощница для опасного</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>офицер особого назначения аудиокнига слушать онлайн бесплатно</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>дуся мерзлякова история жизни и сейчас</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>кунгуров евгений что случилось причина смерти</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>четвертые сутки пылают станицы слушать оригинал</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>жванецкий рассказ подрывника</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>основная мысль рассказа смерть чиновника</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>марков леонид значения</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>особая молитвенная помощь сергий пономарь</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>поддубный евгений евгеньевич личная жизнь</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>сикорский авиаконструктор биография</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>тарас бульба николай гоголь книга персонажи</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Вложенный запрос</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Ярославская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Новосибирская область</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Саратовская область</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Томская область</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Омская область</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Астраханская область</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Ростовская область</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Тульская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ovsyannikovsoap</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ovsyannikovsoap ru</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ovsyannikovsoap ru крем</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ovsyannikovsoap ru мыло</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>23</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ovsyannikovsoap ru мыло крем</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ассоциация</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Ярославская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Новосибирская область</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Саратовская область</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Томская область</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Омская область</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Астраханская область</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Ростовская область</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Тульская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>овсиенко</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14471</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2373</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1632</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1796</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1649</v>
+      </c>
+      <c r="H2" t="n">
+        <v>482</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="J2" t="n">
+        <v>588</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2746</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>единственная моя</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12649</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1378</v>
+      </c>
+      <c r="D3" t="n">
+        <v>876</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1691</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1814</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1429</v>
+      </c>
+      <c r="H3" t="n">
+        <v>344</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1012</v>
+      </c>
+      <c r="J3" t="n">
+        <v>493</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2487</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>никах это</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7144</v>
+      </c>
+      <c r="C4" t="n">
+        <v>732</v>
+      </c>
+      <c r="D4" t="n">
+        <v>444</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1474</v>
+      </c>
+      <c r="F4" t="n">
+        <v>944</v>
+      </c>
+      <c r="G4" t="n">
+        <v>651</v>
+      </c>
+      <c r="H4" t="n">
+        <v>222</v>
+      </c>
+      <c r="I4" t="n">
+        <v>636</v>
+      </c>
+      <c r="J4" t="n">
+        <v>322</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1330</v>
+      </c>
+      <c r="L4" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>мильковский</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4389</v>
+      </c>
+      <c r="C5" t="n">
+        <v>447</v>
+      </c>
+      <c r="D5" t="n">
+        <v>341</v>
+      </c>
+      <c r="E5" t="n">
+        <v>591</v>
+      </c>
+      <c r="F5" t="n">
+        <v>711</v>
+      </c>
+      <c r="G5" t="n">
+        <v>417</v>
+      </c>
+      <c r="H5" t="n">
+        <v>156</v>
+      </c>
+      <c r="I5" t="n">
+        <v>422</v>
+      </c>
+      <c r="J5" t="n">
+        <v>138</v>
+      </c>
+      <c r="K5" t="n">
+        <v>760</v>
+      </c>
+      <c r="L5" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>давай со мной за звездами</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2235</v>
+      </c>
+      <c r="C6" t="n">
+        <v>223</v>
+      </c>
+      <c r="D6" t="n">
+        <v>196</v>
+      </c>
+      <c r="E6" t="n">
+        <v>555</v>
+      </c>
+      <c r="F6" t="n">
+        <v>310</v>
+      </c>
+      <c r="G6" t="n">
+        <v>212</v>
+      </c>
+      <c r="H6" t="n">
+        <v>62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>163</v>
+      </c>
+      <c r="J6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="n">
+        <v>305</v>
+      </c>
+      <c r="L6" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>никах что это</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C7" t="n">
+        <v>198</v>
+      </c>
+      <c r="D7" t="n">
+        <v>129</v>
+      </c>
+      <c r="E7" t="n">
+        <v>418</v>
+      </c>
+      <c r="F7" t="n">
+        <v>253</v>
+      </c>
+      <c r="G7" t="n">
+        <v>203</v>
+      </c>
+      <c r="H7" t="n">
+        <v>62</v>
+      </c>
+      <c r="I7" t="n">
+        <v>176</v>
+      </c>
+      <c r="J7" t="n">
+        <v>65</v>
+      </c>
+      <c r="K7" t="n">
+        <v>346</v>
+      </c>
+      <c r="L7" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>пассия это</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>996</v>
+      </c>
+      <c r="C8" t="n">
+        <v>116</v>
+      </c>
+      <c r="D8" t="n">
+        <v>55</v>
+      </c>
+      <c r="E8" t="n">
+        <v>206</v>
+      </c>
+      <c r="F8" t="n">
+        <v>150</v>
+      </c>
+      <c r="G8" t="n">
+        <v>84</v>
+      </c>
+      <c r="H8" t="n">
+        <v>57</v>
+      </c>
+      <c r="I8" t="n">
+        <v>65</v>
+      </c>
+      <c r="J8" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>175</v>
+      </c>
+      <c r="L8" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>а вы не лезьте в мою душу</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>808</v>
+      </c>
+      <c r="C9" t="n">
+        <v>77</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26</v>
+      </c>
+      <c r="E9" t="n">
+        <v>119</v>
+      </c>
+      <c r="F9" t="n">
+        <v>165</v>
+      </c>
+      <c r="G9" t="n">
+        <v>85</v>
+      </c>
+      <c r="H9" t="n">
+        <v>41</v>
+      </c>
+      <c r="I9" t="n">
+        <v>72</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>зиньковский</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>757</v>
+      </c>
+      <c r="C10" t="n">
+        <v>173</v>
+      </c>
+      <c r="D10" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" t="n">
+        <v>79</v>
+      </c>
+      <c r="F10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G10" t="n">
+        <v>65</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>205</v>
+      </c>
+      <c r="L10" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>кукрыниксы это</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>754</v>
+      </c>
+      <c r="C11" t="n">
+        <v>91</v>
+      </c>
+      <c r="D11" t="n">
+        <v>61</v>
+      </c>
+      <c r="E11" t="n">
+        <v>140</v>
+      </c>
+      <c r="F11" t="n">
+        <v>95</v>
+      </c>
+      <c r="G11" t="n">
+        <v>71</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>62</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>138</v>
+      </c>
+      <c r="L11" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>anikv</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>665</v>
+      </c>
+      <c r="C12" t="n">
+        <v>44</v>
+      </c>
+      <c r="D12" t="n">
+        <v>49</v>
+      </c>
+      <c r="E12" t="n">
+        <v>116</v>
+      </c>
+      <c r="F12" t="n">
+        <v>74</v>
+      </c>
+      <c r="G12" t="n">
+        <v>68</v>
+      </c>
+      <c r="H12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I12" t="n">
+        <v>55</v>
+      </c>
+      <c r="J12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K12" t="n">
+        <v>152</v>
+      </c>
+      <c r="L12" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>власяница</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>646</v>
+      </c>
+      <c r="C13" t="n">
+        <v>72</v>
+      </c>
+      <c r="D13" t="n">
+        <v>36</v>
+      </c>
+      <c r="E13" t="n">
+        <v>114</v>
+      </c>
+      <c r="F13" t="n">
+        <v>134</v>
+      </c>
+      <c r="G13" t="n">
+        <v>80</v>
+      </c>
+      <c r="H13" t="n">
+        <v>28</v>
+      </c>
+      <c r="I13" t="n">
+        <v>39</v>
+      </c>
+      <c r="J13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82</v>
+      </c>
+      <c r="L13" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>анчутка</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>576</v>
+      </c>
+      <c r="C14" t="n">
+        <v>109</v>
+      </c>
+      <c r="D14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E14" t="n">
+        <v>39</v>
+      </c>
+      <c r="F14" t="n">
+        <v>113</v>
+      </c>
+      <c r="G14" t="n">
+        <v>66</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>41</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>78</v>
+      </c>
+      <c r="L14" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>армяк</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>542</v>
+      </c>
+      <c r="C15" t="n">
+        <v>37</v>
+      </c>
+      <c r="D15" t="n">
+        <v>85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>112</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56</v>
+      </c>
+      <c r="G15" t="n">
+        <v>45</v>
+      </c>
+      <c r="H15" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" t="n">
+        <v>29</v>
+      </c>
+      <c r="J15" t="n">
+        <v>45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86</v>
+      </c>
+      <c r="L15" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>новосолошино</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>496</v>
+      </c>
+      <c r="C16" t="n">
+        <v>59</v>
+      </c>
+      <c r="D16" t="n">
+        <v>29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>79</v>
+      </c>
+      <c r="F16" t="n">
+        <v>66</v>
+      </c>
+      <c r="G16" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>29</v>
+      </c>
+      <c r="J16" t="n">
+        <v>21</v>
+      </c>
+      <c r="K16" t="n">
+        <v>107</v>
+      </c>
+      <c r="L16" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>мия бойко все лучшее для меня</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>448</v>
+      </c>
+      <c r="C17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>42</v>
+      </c>
+      <c r="F17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G17" t="n">
+        <v>47</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>47</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K17" t="n">
+        <v>128</v>
+      </c>
+      <c r="L17" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>анчоусы что это такое</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>410</v>
+      </c>
+      <c r="C18" t="n">
+        <v>35</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>46</v>
+      </c>
+      <c r="F18" t="n">
+        <v>81</v>
+      </c>
+      <c r="G18" t="n">
+        <v>42</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>18</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>104</v>
+      </c>
+      <c r="L18" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>мацерация это</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>387</v>
+      </c>
+      <c r="C19" t="n">
+        <v>69</v>
+      </c>
+      <c r="D19" t="n">
+        <v>22</v>
+      </c>
+      <c r="E19" t="n">
+        <v>46</v>
+      </c>
+      <c r="F19" t="n">
+        <v>54</v>
+      </c>
+      <c r="G19" t="n">
+        <v>53</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="n">
+        <v>40</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>упячка</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>303</v>
+      </c>
+      <c r="C20" t="n">
+        <v>41</v>
+      </c>
+      <c r="D20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" t="n">
+        <v>48</v>
+      </c>
+      <c r="G20" t="n">
+        <v>34</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>11</v>
+      </c>
+      <c r="K20" t="n">
+        <v>57</v>
+      </c>
+      <c r="L20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Вложенный запрос</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тюменская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Липецкая область</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Новосибирская область</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Кемеровская область</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Кировская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ovsyannikov</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ovsyannikov soap</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ассоциация</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тюменская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Липецкая область</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Новосибирская область</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Кемеровская область</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Кировская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>евгеника</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>4863</v>
+      </c>
+      <c r="C2" t="n">
+        <v>486</v>
+      </c>
+      <c r="D2" t="n">
+        <v>827</v>
+      </c>
+      <c r="E2" t="n">
+        <v>357</v>
+      </c>
+      <c r="F2" t="n">
+        <v>657</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1094</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="I2" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>анастасян</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3633</v>
+      </c>
+      <c r="C3" t="n">
+        <v>260</v>
+      </c>
+      <c r="D3" t="n">
+        <v>602</v>
+      </c>
+      <c r="E3" t="n">
+        <v>348</v>
+      </c>
+      <c r="F3" t="n">
+        <v>941</v>
+      </c>
+      <c r="G3" t="n">
+        <v>594</v>
+      </c>
+      <c r="H3" t="n">
+        <v>552</v>
+      </c>
+      <c r="I3" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>пюник</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>562</v>
+      </c>
+      <c r="C4" t="n">
+        <v>84</v>
+      </c>
+      <c r="D4" t="n">
+        <v>109</v>
+      </c>
+      <c r="E4" t="n">
+        <v>41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>102</v>
+      </c>
+      <c r="G4" t="n">
+        <v>122</v>
+      </c>
+      <c r="H4" t="n">
+        <v>46</v>
+      </c>
+      <c r="I4" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>пшенников</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>192</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>яишницу</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>153</v>
+      </c>
+      <c r="C6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>34</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>irynakournikova</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>85</v>
+      </c>
+      <c r="C7" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>39</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sh0tnik</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>щаница</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>34</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>юмнико</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>korobeynikov</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>жконика</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>эуоника</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aynikorgg</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>факеравтогрупп</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6569,4 +10015,375 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Вложенный запрос</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>всего</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Тюменская область</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Волгоградская область</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Воронежская область</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Мордовия</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Орловская область</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Рязанская область</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Ярославская область</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Костромская область</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Новосибирская область</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Саратовская область</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Томская область</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Вологодская область</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Алтайский край</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Омская область</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Кемеровская область</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Кировская область</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Пензенская область</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Ростовская область</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Тульская область</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>сайт овсянникова</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>106</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>19</v>
+      </c>
+      <c r="M2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>овсянников официальный сайт</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>овсянников косметика официальный сайт</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>6</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>овсянников мыло официальный сайт</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>овсянников косметика и парфюмерия официальный сайт</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>